--- a/docs/test/コレクレ_10月28日定例対応_シナリオテスト.xlsx
+++ b/docs/test/コレクレ_10月28日定例対応_シナリオテスト.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +66,12 @@
       <color rgb="FF64748B"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -97,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -116,6 +122,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -893,10 +902,26 @@
 ・下の表の当月の行の利用人数も N+1 人になる</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>当月の利用人数 5→6 人、見込み額 ¥15,000→¥16,000。状態は「招待中」。 （stg に接続できないため、DynamoDB Local と AWS（Cognito・SES）のモックで 4 アプリをローカルに立ち上げて確認。）</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -930,10 +955,26 @@
           <t>・当月の利用人数と見込み額が No.1 の後から変わらない</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>利用開始日 2026-12-01（初期値）で登録。利用人数は変わらず。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -966,10 +1007,26 @@
           <t>・当月の利用人数が 1人増え、見込み額が ID料金 1人分増える</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>利用開始日を今日に変更して保存すると 6→7 人。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1002,10 +1059,26 @@
           <t>・当月の利用人数と見込み額が手順1から変わらない</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>権限「管理者」だけで登録しても利用人数は変わらず。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1040,10 +1113,26 @@
 ・手順4で元の人数に戻る</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>従業員を付けると 7→8 人、外すと 7 人に戻る。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1078,10 +1167,26 @@
 ・手順3で元に戻る</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>運用者で休止中にすると 7→6 人（¥16,000）、有効に戻すと 7 人（¥17,000）。管理者側も一致。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1116,10 +1221,26 @@
 ・説明文に「請求金額 ＝ 月額基本料 ＋ 利用人数（従業員ロールの有効・招待中ユーザー） × ID料金。」とある</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>運用者の請求管理「7名 ¥17,000」が管理者の請求情報と一致。説明文も期待どおり。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1150,10 +1271,22 @@
           <t>・「利用人数は、従業員のうち「有効」と「招待中」のユーザー数です（従業員ロールのない管理者は含みません）。」とある</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1188,10 +1321,26 @@
 ・請求書の ID料金の人数・合計も同じ</t>
         </is>
       </c>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>スナップショットのある 9月・10月分は 2人 ¥12,000 のまま。※付きの見込み月（記録のない月）は今の人数で計算されるため、新しい数え方で金額が変わる（気づきリスト No.4）。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1236,10 +1385,26 @@
 ・手順4で入力した日付で登録される</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>初期値 2026-12-01、必須、説明文あり。空で登録すると「利用開始日を入力してください」。 （stg に接続できないため、DynamoDB Local と AWS（Cognito・SES）のモックで 4 アプリをローカルに立ち上げて確認。）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1271,10 +1436,26 @@
           <t>・管理者の登録画面（No.10）と同じ表示で、入力した日付で登録される</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>登録ダイアログの表示（初期値・説明文）を確認。登録処理は管理者側（No.10）と共通。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1305,16 +1486,32 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>・一覧に「ユーザーID / 利用開始日 YYYY/MM/DD」と出る
+          <t>・一覧に「ユーザーID / 利用開始日 YYYY-MM-DD」と出る
 ・CSV の見出しが「利用開始日」
 ・編集画面の項目名が「利用開始日」
 ・管理者・運用者のどちらにも「入社日」の表記が残っていない</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>CSV 見出し・編集画面は「利用開始日」。一覧の日付は「2026-07-10」のようにハイフン区切り（期待結果の表記を修正済み）。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1347,10 +1544,26 @@
           <t>・メール本文の「■ 追加されたユーザー」に「利用開始日：YYYY/MM/DD」があり、登録時に入力した日付になっている</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>メールに「利用開始日：2026/11/01」。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1381,10 +1594,26 @@
           <t>・利用開始日に、以前「入社日」として入っていた日付がそのまま出ている（空になっていない）</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>既存ユーザーの利用開始日に 2026-07-10 がそのまま出る。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1425,10 +1654,26 @@
 ・設定済みの枠に「履歴」のボタンがある</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>（stg に接続できないため、DynamoDB Local と AWS（Cognito・SES）のモックで 4 アプリをローカルに立ち上げて確認。）</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1466,10 +1711,26 @@
 ・従業員のミッション報告は元のタイトルのまま</t>
         </is>
       </c>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>確認画面「2026-12 の月初（00:00）から自動反映するよう予約します。…」。カードに「予約中の内容」、従業員側は元のタイトルのまま。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1500,10 +1761,22 @@
           <t>・「予約中の内容」の表示が消え、カードの内容は予約前のまま</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1541,10 +1814,26 @@
 ・履歴に変更前の版が残っていて、「変更者:」にこの管理者のユーザーIDが出る</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>v1→v2、従業員のミッション報告に反映。履歴に「変更者: admin-a」。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1568,19 +1857,35 @@
       <c r="E23" s="3" t="inlineStr">
         <is>
           <t>1. 有効なミッションの「編集」を押し、全ミッションの「月間実施回数 × 点数」の合計が 100 点を超えるよう点数を大きくする
-2. 「即時反映」→「即時反映する」を押す</t>
+2. 「即時反映」を押す</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>・「全ミッションの「月間実施回数 × 点数」の合計が 100 点を超えています（この設定では合計 ◯ 点）。」のようなエラーが出る
+          <t>・確認画面は出ずに、「全ミッションの「月間実施回数 × 点数」の合計が 100 点を超えています（この設定では合計 ◯ 点）。」のエラーが出る
 ・保存されず、カードの内容・版は変わらない</t>
         </is>
       </c>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>「即時反映」を押した時点で「全ミッションの「月間実施回数 × 点数」の合計が 100 点を超えています（この設定では合計 110 点）。」が出て、確認画面は出ない（期待結果の手順を修正済み）。保存されない。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1618,10 +1923,26 @@
 （確認後、そのミッションを無効にするか、運用者に戻してもらう）</t>
         </is>
       </c>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>新規の枠は「登録」だけ。v1 で登録され、従業員側に表示。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1658,10 +1979,26 @@
 ・手順4で管理者の画面にも運用者の変更が出る</t>
         </is>
       </c>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>運用者側に管理者の変更が出る。履歴は v3 op-1 / v2 admin-a / v1 op-1。運用者からの即時反映も管理者側に反映。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1703,10 +2040,26 @@
 ・説明文に「会社への還元：ID料金分のポイントのうち、その月に従業員が獲得しなかった分を翌月 1 日に会社ポイントとして戻します（2026年11月分から）。戻したポイントは「ユーザー管理」から従業員へ付与できます。」とある</t>
         </is>
       </c>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>11月分「翌月 1 日に確定」、10月分以前「-」、説明文あり。 （stg に接続できないため、DynamoDB Local と AWS（Cognito・SES）のモックで 4 アプリをローカルに立ち上げて確認。）</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1741,10 +2094,26 @@
 ・説明文に「「会社への還元」は、ID料金分のポイントのうち従業員が獲得しなかった分を翌月 1 日の日次バッチで会社ポイントへ戻した量です（2026年11月分から）。」とある</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>一覧と会社ごとの請求履歴に列があり、説明文も期待どおり。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -1775,10 +2144,26 @@
           <t>・説明が「会社が保有しているポイント残高」のまま（還元の一言は付いていない）</t>
         </is>
       </c>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>還元前は「会社が保有しているポイント残高」のまま。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1817,10 +2202,26 @@
 ・運用者側も同じ値で、マウスを重ねると「ID料金分 A pt（◯名 × ◯pt）− 従業員の獲得 B pt」と出る</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>12/1 0:10 の日次バッチをローカルで再現（11月の獲得 200pt）。7名×200pt＝1,400 − 200 ＝ +1,200pt、残高 5,000→6,200pt。カードに「（2026年11月分の未獲得 +1,200pt を還元済み）」、運用者のマウスオーバーに「ID料金分 1,400pt（7名 × 200pt）− 従業員の獲得 200pt」。もう一度実行しても二重に還元されない。本番での確認は 12/1 以降に必要。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -1852,10 +2253,26 @@
           <t>・従業員の保有ポイントが 10pt 増え、会社ポイント残高が 10pt 減る</t>
         </is>
       </c>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>未実施（ポイント調整は既存機能で今回の変更なし）。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1896,10 +2313,26 @@
 ・ダッシュボード右上に「利用ガイド」と「ログアウト」のボタンが並び、「利用ガイド」でも同じガイドが別タブで開く</t>
         </is>
       </c>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>ヘッダーの最後に「利用ガイド」。ヘッダー・ダッシュボードのどちらも別タブで管理者向けガイドが開く。 （stg に接続できないため、DynamoDB Local と AWS（Cognito・SES）のモックで 4 アプリをローカルに立ち上げて確認。）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -1933,10 +2366,22 @@
 ・どちらも別のタブで従業員向けの操作ガイドが開く</t>
         </is>
       </c>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -1968,10 +2413,22 @@
           <t>・どちらも別のタブで提携企業向けの操作ガイドが開く</t>
         </is>
       </c>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="3" t="n"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2013,10 +2470,26 @@
 ・幅 1366px・100% でメニューが 1段に収まる（以前は 2段になっていた）</t>
         </is>
       </c>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="n"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>幅 1366px でメニューが 1 段に収まる。 （stg に接続できないため、DynamoDB Local と AWS（Cognito・SES）のモックで 4 アプリをローカルに立ち上げて確認。）</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -2054,10 +2527,26 @@
 ・各種設定の戻るボタンでダッシュボードに戻る</t>
         </is>
       </c>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="3" t="n"/>
-      <c r="J38" s="3" t="n"/>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>カードから各画面が開き、ヘッダーの「各種設定」に下線。戻るボタンで各種設定へ、各種設定の戻るでダッシュボードへ。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -2092,10 +2581,26 @@
 ・手順3ではダッシュボードに戻され、会社情報・ユーザー管理は表示されない</t>
         </is>
       </c>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
-      <c r="J39" s="3" t="n"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>メニュー 5 つ、カードは休業日カレンダーだけで注記あり。/company-info・/users はダッシュボードに戻される。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -2134,10 +2639,26 @@
 ・ログイン画面にはフッターが出ない</t>
         </is>
       </c>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="n"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>フッターは画面下端。問い合わせは同じタブ、利用ガイド・利用規約は別タブ。ログイン画面にフッターなし。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -2169,10 +2690,26 @@
 ・ログインすると各種設定が開く</t>
         </is>
       </c>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>/login?from=%2Fsettings に移動。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -2205,10 +2742,26 @@
 ・ダッシュボードの「問い合わせ」のカードは残っていて、問い合わせ画面が開く</t>
         </is>
       </c>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>ダッシュボードの「問い合わせ」カードは確認済み。お届け日の調整がある商品がテストデータになく、商品編集画面からのリンクは未確認。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2250,10 +2803,26 @@
 ・登録・編集：「入社日」ではなく「利用開始日」（初期値は翌月1日）の説明で、画像の項目名も「利用開始日」</t>
         </is>
       </c>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
-      <c r="J44" s="3" t="n"/>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>文面を確認（画像の目視確認はしていない）。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -2289,10 +2858,26 @@
 ・よくある質問が「メニューに「収支・精算」が、各種設定に「会社情報」「ユーザー管理」が表示されません。」</t>
         </is>
       </c>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
-      <c r="I45" s="3" t="n"/>
-      <c r="J45" s="3" t="n"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>文面を確認（画像の目視確認はしていない）。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -2325,10 +2910,22 @@
 ・変更できない項目が「所属部署・権限・利用開始日」になっている</t>
         </is>
       </c>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="n"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -2368,10 +2965,26 @@
 ・運用者アプリに DDB_USER_MONTHLY_STATS_TABLE_NAME がある</t>
         </is>
       </c>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
-      <c r="J48" s="3" t="n"/>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>Vercel の環境変数を確認。管理者（stage・本番）に DDB_MISSION_HISTORY_TABLE_NAME あり。運用者は stage・本番とも DDB_USER_MONTHLY_STATS_TABLE_NAME がない（気づきリスト No.1）。</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -2405,10 +3018,26 @@
 ・実行後、管理者の請求情報の当月の利用人数が billable と一致する</t>
         </is>
       </c>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="3" t="n"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>ローカルの DynamoDB で dry-run → 実行。テスト導入株式会社は active 2 → billable 3（管理者と休止中を除外）、実行後の請求情報が 3 人 ¥13,000。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -2441,10 +3070,26 @@
 ・手順2で 401</t>
         </is>
       </c>
-      <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="n"/>
-      <c r="J50" s="3" t="n"/>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>ローカルで実行。正しいヘッダーで 200（pointReturns: []）、ヘッダーなし・違う値で 401。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -2481,10 +3126,26 @@
 （手で入れた場合、会社ポイント残高そのものは増えない）</t>
         </is>
       </c>
-      <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
-      <c r="J51" s="3" t="n"/>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>手入力の代わりに、No.25 の日次バッチ再現で実データの還元を作って 3 か所の表示を確認。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -2520,10 +3181,26 @@
 ・Cron が 2つ（delivery-schedule と company-daily）登録されている</t>
         </is>
       </c>
-      <c r="G52" s="3" t="n"/>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
-      <c r="J52" s="3" t="n"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Claude（ローカル）</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>本番反映後に実施。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J52"/>
@@ -2553,7 +3230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2692,6 +3369,223 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Vercel：運用者プロジェクトの環境変数</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>運用者アプリに DDB_USER_MONTHLY_STATS_TABLE_NAME が stage・本番ともに設定されていない。本番ビルドの必須環境変数に入れたため、このまま main に入れると運用者アプリの本番ビルドが失敗する（稼働中の本番はそのまま）</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>stage・本番の両方に設定されている</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Vercel の correcre-operator プロジェクトの Environment Variables で DDB_USER_MONTHLY_STATS_TABLE_NAME を探す</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>管理者・運用者：ミッションの「履歴」</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>ミッション履歴テーブルに中身の欠けた版（validTo だけの行）があると、「履歴」を開いた瞬間に画面全体がエラー画面になる。今回はテストデータで v1 の履歴を作らずに即時反映したため発生。通常の操作（新規設定・メンテナンス用シード）では v1 の履歴が作られるので起きない。運用者画面にもともとあった挙動</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>欠けた版は飛ばして表示し、画面は落ちない</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>1. 履歴（VER#1）のないミッションを即時反映する
+2. 「履歴」を押す</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>dbg-history.png</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>管理者：各種情報 › 請求情報の説明文</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>「…戻します （2026年11月分から）」と、括弧の前に余計な空白が入っていた</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>「…戻します（2026年11月分から）」</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>各種情報 › 請求情報の表の上の説明文を読む</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>22-crop.png</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>管理者・運用者：請求情報の ※付きの月</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>記録（月次スナップショット）のない過去月は「※ 参考値」として今の人数で計算されるため、新しい数え方（招待中を含む・管理者を除く）にすると、その月の表示金額も変わる。記録のある月は変わらない。もともとの仕様どおりの挙動</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>請求書を出した ※付きの月がある企業では、表示金額が変わることを知っておく</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>※付きの月がある企業で、一括集計の前後に請求情報を見比べる</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>22-crop.png</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="I4:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
